--- a/www/flightdata/xlsx/eoss-292.xlsx
+++ b/www/flightdata/xlsx/eoss-292.xlsx
@@ -5526,7 +5526,7 @@
         <v>32628.84</v>
       </c>
       <c r="I2">
-        <v>1017</v>
+        <v>784</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
